--- a/src/test/output_test/Over_counts_regions/Region_over_0_10/Stats_over_0_10.xlsx
+++ b/src/test/output_test/Over_counts_regions/Region_over_0_10/Stats_over_0_10.xlsx
@@ -522,49 +522,49 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>89359</v>
+        <v>89413</v>
       </c>
       <c r="G2">
-        <v>255887.2697338873</v>
+        <v>268239</v>
       </c>
       <c r="H2">
-        <v>255.8872697338873</v>
+        <v>268.239</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
       <c r="J2">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="K2">
-        <v>57.46374735617005</v>
+        <v>56.89119031908112</v>
       </c>
       <c r="L2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M2">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="N2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="O2">
-        <v>31.90864598119769</v>
+        <v>31.44913203381839</v>
       </c>
       <c r="P2">
-        <v>0.617499147560965</v>
+        <v>0.631151221203839</v>
       </c>
       <c r="Q2">
-        <v>0.310516007252835</v>
+        <v>0.3820459283597004</v>
       </c>
       <c r="R2">
         <v>18</v>
@@ -573,13 +573,13 @@
         <v>33</v>
       </c>
       <c r="T2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="V2">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
